--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/56.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/56.xlsx
@@ -426,13 +426,13 @@
         <v>-9.083562478384199</v>
       </c>
       <c r="E2">
-        <v>-24.2434503282633</v>
+        <v>-24.13152456468972</v>
       </c>
       <c r="F2">
-        <v>-4.786196827758479</v>
+        <v>-4.696950180515666</v>
       </c>
       <c r="G2">
-        <v>-13.44472579439123</v>
+        <v>-13.40643933522956</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.785447203980237</v>
       </c>
       <c r="E3">
-        <v>-22.39907079204928</v>
+        <v>-26.30652798820376</v>
       </c>
       <c r="F3">
-        <v>-4.257502930065334</v>
+        <v>-4.42590919468707</v>
       </c>
       <c r="G3">
-        <v>-13.38898282860098</v>
+        <v>-12.60059296115125</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.405505968562252</v>
       </c>
       <c r="E4">
-        <v>-25.21843983906275</v>
+        <v>-26.90767385577398</v>
       </c>
       <c r="F4">
-        <v>-4.738906161100058</v>
+        <v>-3.814273354053819</v>
       </c>
       <c r="G4">
-        <v>-13.92942773261424</v>
+        <v>-13.38303708881245</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.966625487879191</v>
       </c>
       <c r="E5">
-        <v>-24.97737558221243</v>
+        <v>-26.71171320004007</v>
       </c>
       <c r="F5">
-        <v>-3.918836514574395</v>
+        <v>-4.535295938594148</v>
       </c>
       <c r="G5">
-        <v>-13.3584000089092</v>
+        <v>-12.86379457370546</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.480624367088237</v>
       </c>
       <c r="E6">
-        <v>-24.6259569422692</v>
+        <v>-25.61280652649473</v>
       </c>
       <c r="F6">
-        <v>-4.814575038243584</v>
+        <v>-4.372503519861183</v>
       </c>
       <c r="G6">
-        <v>-12.27658655867724</v>
+        <v>-13.66377466108819</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.96518797541774</v>
       </c>
       <c r="E7">
-        <v>-24.44486779517647</v>
+        <v>-25.87060802327739</v>
       </c>
       <c r="F7">
-        <v>-4.537804235089824</v>
+        <v>-3.893719586554111</v>
       </c>
       <c r="G7">
-        <v>-11.90686483285143</v>
+        <v>-14.65430809443859</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.431649297454272</v>
       </c>
       <c r="E8">
-        <v>-24.50723846768411</v>
+        <v>-24.4898128997026</v>
       </c>
       <c r="F8">
-        <v>-3.959683311206438</v>
+        <v>-3.989635419756863</v>
       </c>
       <c r="G8">
-        <v>-13.23331435625338</v>
+        <v>-12.94545248997713</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.892711250379478</v>
       </c>
       <c r="E9">
-        <v>-26.3193616835415</v>
+        <v>-26.82340801143926</v>
       </c>
       <c r="F9">
-        <v>-3.952882414829455</v>
+        <v>-3.491065102666522</v>
       </c>
       <c r="G9">
-        <v>-12.957833930294</v>
+        <v>-11.94702506078833</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.357538292860056</v>
       </c>
       <c r="E10">
-        <v>-25.02085798963408</v>
+        <v>-25.64837768982498</v>
       </c>
       <c r="F10">
-        <v>-4.243122471952734</v>
+        <v>-4.033458540467166</v>
       </c>
       <c r="G10">
-        <v>-13.20901495199512</v>
+        <v>-13.49542017823409</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.833703166376668</v>
       </c>
       <c r="E11">
-        <v>-25.27167205102291</v>
+        <v>-26.61829983820984</v>
       </c>
       <c r="F11">
-        <v>-4.117218910401237</v>
+        <v>-4.008618287159416</v>
       </c>
       <c r="G11">
-        <v>-12.23127843242677</v>
+        <v>-12.86756859562023</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.326170356677783</v>
       </c>
       <c r="E12">
-        <v>-26.06504711174474</v>
+        <v>-27.32523991554726</v>
       </c>
       <c r="F12">
-        <v>-4.100871079706989</v>
+        <v>-3.250102137233577</v>
       </c>
       <c r="G12">
-        <v>-12.05338295732849</v>
+        <v>-13.13213746348217</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.836627995899597</v>
       </c>
       <c r="E13">
-        <v>-25.95534482890892</v>
+        <v>-28.32178043414921</v>
       </c>
       <c r="F13">
-        <v>-3.234758287831521</v>
+        <v>-2.863368046460391</v>
       </c>
       <c r="G13">
-        <v>-12.69515869448053</v>
+        <v>-12.69596315704657</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.373570741059682</v>
       </c>
       <c r="E14">
-        <v>-24.08496732341687</v>
+        <v>-26.3941675456742</v>
       </c>
       <c r="F14">
-        <v>-3.455952265196657</v>
+        <v>-2.919074097563852</v>
       </c>
       <c r="G14">
-        <v>-10.68907072459391</v>
+        <v>-12.79537552904535</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.942111942783543</v>
       </c>
       <c r="E15">
-        <v>-26.25336823182772</v>
+        <v>-27.7551822947835</v>
       </c>
       <c r="F15">
-        <v>-3.578008888529552</v>
+        <v>-3.541486998107525</v>
       </c>
       <c r="G15">
-        <v>-12.04391479708618</v>
+        <v>-12.17780319033092</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.547140921424939</v>
       </c>
       <c r="E16">
-        <v>-26.70666847999552</v>
+        <v>-28.1702259945345</v>
       </c>
       <c r="F16">
-        <v>-3.104652418445622</v>
+        <v>-2.586346247983583</v>
       </c>
       <c r="G16">
-        <v>-13.27599390934566</v>
+        <v>-12.38395086106134</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.193671298756943</v>
       </c>
       <c r="E17">
-        <v>-27.90425060216799</v>
+        <v>-30.43511509862678</v>
       </c>
       <c r="F17">
-        <v>-3.673090555757685</v>
+        <v>-2.468966587006893</v>
       </c>
       <c r="G17">
-        <v>-11.1131648503567</v>
+        <v>-12.69885657384789</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.885636790875453</v>
       </c>
       <c r="E18">
-        <v>-26.53349963394221</v>
+        <v>-30.17184999795387</v>
       </c>
       <c r="F18">
-        <v>-3.786626591985385</v>
+        <v>-2.58435402437985</v>
       </c>
       <c r="G18">
-        <v>-10.73614668216234</v>
+        <v>-12.42741170290089</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.625421621785103</v>
       </c>
       <c r="E19">
-        <v>-27.28166693864545</v>
+        <v>-27.51274138183485</v>
       </c>
       <c r="F19">
-        <v>-2.718652261191317</v>
+        <v>-1.869236042686676</v>
       </c>
       <c r="G19">
-        <v>-11.3215868658726</v>
+        <v>-11.57067231224736</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.41316091435318</v>
       </c>
       <c r="E20">
-        <v>-28.57963627261996</v>
+        <v>-26.73629828542771</v>
       </c>
       <c r="F20">
-        <v>-2.980204298420844</v>
+        <v>-2.586399263497362</v>
       </c>
       <c r="G20">
-        <v>-11.3374940371888</v>
+        <v>-12.71330710512681</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.247638654896226</v>
       </c>
       <c r="E21">
-        <v>-27.65556039508876</v>
+        <v>-30.23341233785114</v>
       </c>
       <c r="F21">
-        <v>-2.638055426368537</v>
+        <v>-1.919911418552936</v>
       </c>
       <c r="G21">
-        <v>-11.17051674127904</v>
+        <v>-11.38546715259838</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.128998599831</v>
       </c>
       <c r="E22">
-        <v>-27.84020439427751</v>
+        <v>-28.25227288660547</v>
       </c>
       <c r="F22">
-        <v>-2.499464589675763</v>
+        <v>-1.679394943150099</v>
       </c>
       <c r="G22">
-        <v>-11.04964210254917</v>
+        <v>-12.37113573927882</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.055010585650777</v>
       </c>
       <c r="E23">
-        <v>-27.09173368181575</v>
+        <v>-29.07122929699663</v>
       </c>
       <c r="F23">
-        <v>-2.670291343848479</v>
+        <v>-2.594012788296492</v>
       </c>
       <c r="G23">
-        <v>-10.48692550342047</v>
+        <v>-11.18455676491109</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.022364222717445</v>
       </c>
       <c r="E24">
-        <v>-28.4427450318421</v>
+        <v>-30.34854199678515</v>
       </c>
       <c r="F24">
-        <v>-2.406935122415655</v>
+        <v>-1.90030644723088</v>
       </c>
       <c r="G24">
-        <v>-11.17693257853414</v>
+        <v>-11.46562870228629</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.028616298341835</v>
       </c>
       <c r="E25">
-        <v>-27.09274353151946</v>
+        <v>-29.62051734446802</v>
       </c>
       <c r="F25">
-        <v>-2.705081118031253</v>
+        <v>-2.199341281069682</v>
       </c>
       <c r="G25">
-        <v>-11.14604518865274</v>
+        <v>-12.01456018978946</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.070638132558406</v>
       </c>
       <c r="E26">
-        <v>-27.81201011510575</v>
+        <v>-28.27743308819209</v>
       </c>
       <c r="F26">
-        <v>-2.587270706005107</v>
+        <v>-2.53703105139272</v>
       </c>
       <c r="G26">
-        <v>-11.17649558652296</v>
+        <v>-12.31185048976155</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.145088268874862</v>
       </c>
       <c r="E27">
-        <v>-27.79451662001413</v>
+        <v>-28.91088056085903</v>
       </c>
       <c r="F27">
-        <v>-2.923579587867679</v>
+        <v>-2.754592637696579</v>
       </c>
       <c r="G27">
-        <v>-11.14245986783371</v>
+        <v>-12.48368435597743</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.248319664648796</v>
       </c>
       <c r="E28">
-        <v>-27.48642189090227</v>
+        <v>-27.28268584529718</v>
       </c>
       <c r="F28">
-        <v>-3.181629287718169</v>
+        <v>-2.424874246890681</v>
       </c>
       <c r="G28">
-        <v>-10.63571135159193</v>
+        <v>-12.4250347312037</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.377363241484133</v>
       </c>
       <c r="E29">
-        <v>-26.88547527618838</v>
+        <v>-28.25525262250252</v>
       </c>
       <c r="F29">
-        <v>-2.460187549272024</v>
+        <v>-2.086933481244595</v>
       </c>
       <c r="G29">
-        <v>-11.89905194537875</v>
+        <v>-13.5217224625436</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.529206822371867</v>
       </c>
       <c r="E30">
-        <v>-26.5513237076364</v>
+        <v>-29.29155767136582</v>
       </c>
       <c r="F30">
-        <v>-2.618775175068378</v>
+        <v>-2.145310188854681</v>
       </c>
       <c r="G30">
-        <v>-11.58691715920857</v>
+        <v>-13.13605052830959</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.700140921267756</v>
       </c>
       <c r="E31">
-        <v>-26.0777766521803</v>
+        <v>-27.80491852480974</v>
       </c>
       <c r="F31">
-        <v>-2.47053385813299</v>
+        <v>-1.874561616719274</v>
       </c>
       <c r="G31">
-        <v>-11.37076501985847</v>
+        <v>-14.13417669785431</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.885411115677971</v>
       </c>
       <c r="E32">
-        <v>-24.66669056596819</v>
+        <v>-28.11151432902506</v>
       </c>
       <c r="F32">
-        <v>-2.694913736529292</v>
+        <v>-2.329464546171039</v>
       </c>
       <c r="G32">
-        <v>-12.32704589378681</v>
+        <v>-13.20878983489845</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.082376370935567</v>
       </c>
       <c r="E33">
-        <v>-26.60384947765137</v>
+        <v>-29.03730649820517</v>
       </c>
       <c r="F33">
-        <v>-2.664880447973393</v>
+        <v>-2.269307677012336</v>
       </c>
       <c r="G33">
-        <v>-11.85804090723826</v>
+        <v>-11.69501309215685</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.28714212375116</v>
       </c>
       <c r="E34">
-        <v>-25.6132005037334</v>
+        <v>-26.2888397687298</v>
       </c>
       <c r="F34">
-        <v>-2.920445045615485</v>
+        <v>-2.770090563435555</v>
       </c>
       <c r="G34">
-        <v>-11.64794375567949</v>
+        <v>-12.5537686050438</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.495870942045607</v>
       </c>
       <c r="E35">
-        <v>-23.18347947423592</v>
+        <v>-25.51556660412803</v>
       </c>
       <c r="F35">
-        <v>-2.767016492003767</v>
+        <v>-2.867709520018463</v>
       </c>
       <c r="G35">
-        <v>-13.08346251241827</v>
+        <v>-12.23601251254793</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.704234778031738</v>
       </c>
       <c r="E36">
-        <v>-24.98510568734353</v>
+        <v>-25.79425795150807</v>
       </c>
       <c r="F36">
-        <v>-2.736849007928614</v>
+        <v>-2.308795122736386</v>
       </c>
       <c r="G36">
-        <v>-12.40049365712108</v>
+        <v>-13.36751063023327</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.90817348714298</v>
       </c>
       <c r="E37">
-        <v>-23.91476462783858</v>
+        <v>-25.72937397592617</v>
       </c>
       <c r="F37">
-        <v>-2.526965559081303</v>
+        <v>-2.566111717435399</v>
       </c>
       <c r="G37">
-        <v>-11.93613998705521</v>
+        <v>-13.63965899210737</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.10325245251355</v>
       </c>
       <c r="E38">
-        <v>-24.90236593874938</v>
+        <v>-26.06025145777062</v>
       </c>
       <c r="F38">
-        <v>-3.000835616954969</v>
+        <v>-2.225979920008908</v>
       </c>
       <c r="G38">
-        <v>-11.71617740978941</v>
+        <v>-13.30579875083572</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.284404596801789</v>
       </c>
       <c r="E39">
-        <v>-23.546024574816</v>
+        <v>-23.73496609583803</v>
       </c>
       <c r="F39">
-        <v>-2.840807460245146</v>
+        <v>-1.778924943331266</v>
       </c>
       <c r="G39">
-        <v>-12.23961438609466</v>
+        <v>-12.03807499475491</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.447019785677346</v>
       </c>
       <c r="E40">
-        <v>-23.71583329315563</v>
+        <v>-24.8693760056035</v>
       </c>
       <c r="F40">
-        <v>-2.903745158775047</v>
+        <v>-2.147452346958321</v>
       </c>
       <c r="G40">
-        <v>-11.8723755694233</v>
+        <v>-12.865989465398</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.588974274796572</v>
       </c>
       <c r="E41">
-        <v>-22.76690967874433</v>
+        <v>-23.97036976017876</v>
       </c>
       <c r="F41">
-        <v>-2.610440970628812</v>
+        <v>-3.037775004548007</v>
       </c>
       <c r="G41">
-        <v>-10.92027260396553</v>
+        <v>-13.66059322682495</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.708505213315285</v>
       </c>
       <c r="E42">
-        <v>-24.35267712132832</v>
+        <v>-24.96243161798712</v>
       </c>
       <c r="F42">
-        <v>-2.495250684697721</v>
+        <v>-3.458328851275288</v>
       </c>
       <c r="G42">
-        <v>-10.72325872837796</v>
+        <v>-11.51139037327563</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.804996700432805</v>
       </c>
       <c r="E43">
-        <v>-22.89953962548098</v>
+        <v>-25.8867882609068</v>
       </c>
       <c r="F43">
-        <v>-2.83391710018866</v>
+        <v>-2.356835461894341</v>
       </c>
       <c r="G43">
-        <v>-11.87807963938747</v>
+        <v>-10.3336969031353</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.87869094161808</v>
       </c>
       <c r="E44">
-        <v>-23.42982393177918</v>
+        <v>-23.27130922761469</v>
       </c>
       <c r="F44">
-        <v>-3.076490411852648</v>
+        <v>-3.060619720782412</v>
       </c>
       <c r="G44">
-        <v>-10.34569763071516</v>
+        <v>-11.71630983161098</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.932421613960159</v>
       </c>
       <c r="E45">
-        <v>-21.00321849239898</v>
+        <v>-22.09169609030465</v>
       </c>
       <c r="F45">
-        <v>-3.107638682932715</v>
+        <v>-2.473277410971062</v>
       </c>
       <c r="G45">
-        <v>-11.01279904124262</v>
+        <v>-11.70966225616812</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.969460924133659</v>
       </c>
       <c r="E46">
-        <v>-22.46281359218125</v>
+        <v>-25.4062130137908</v>
       </c>
       <c r="F46">
-        <v>-2.940001143260776</v>
+        <v>-2.775994337915308</v>
       </c>
       <c r="G46">
-        <v>-11.77017571808046</v>
+        <v>-12.26214926958048</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.992573919770276</v>
       </c>
       <c r="E47">
-        <v>-20.0848801914355</v>
+        <v>-24.66886423349187</v>
       </c>
       <c r="F47">
-        <v>-3.073061799172461</v>
+        <v>-2.119359094859778</v>
       </c>
       <c r="G47">
-        <v>-10.11802810343394</v>
+        <v>-11.29421196480837</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.006371231250935</v>
       </c>
       <c r="E48">
-        <v>-21.68856227719382</v>
+        <v>-23.23037635105936</v>
       </c>
       <c r="F48">
-        <v>-2.870316392235073</v>
+        <v>-2.680634339239834</v>
       </c>
       <c r="G48">
-        <v>-8.983130055479768</v>
+        <v>-12.40893554824622</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.016581409353002</v>
       </c>
       <c r="E49">
-        <v>-20.81514190991242</v>
+        <v>-22.19655743442626</v>
       </c>
       <c r="F49">
-        <v>-3.359252796430856</v>
+        <v>-2.874770523759926</v>
       </c>
       <c r="G49">
-        <v>-10.17298315938584</v>
+        <v>-11.5624058800358</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.028720833121461</v>
       </c>
       <c r="E50">
-        <v>-21.31469599159456</v>
+        <v>-22.89089929707434</v>
       </c>
       <c r="F50">
-        <v>-3.433333693263216</v>
+        <v>-2.928568016367337</v>
       </c>
       <c r="G50">
-        <v>-10.5080202995967</v>
+        <v>-10.48752471216308</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.048085819697098</v>
       </c>
       <c r="E51">
-        <v>-19.49822091221581</v>
+        <v>-23.7015912424015</v>
       </c>
       <c r="F51">
-        <v>-3.593061980973225</v>
+        <v>-2.702052606806618</v>
       </c>
       <c r="G51">
-        <v>-9.189840518951861</v>
+        <v>-11.88516089629597</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.078831539338403</v>
       </c>
       <c r="E52">
-        <v>-20.96714919692788</v>
+        <v>-23.19148128780747</v>
       </c>
       <c r="F52">
-        <v>-3.441889900166732</v>
+        <v>-3.163864120397731</v>
       </c>
       <c r="G52">
-        <v>-10.58782762091192</v>
+        <v>-11.77628698514596</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.126194173874285</v>
       </c>
       <c r="E53">
-        <v>-20.80954924451294</v>
+        <v>-22.08230403521274</v>
       </c>
       <c r="F53">
-        <v>-3.953135066887309</v>
+        <v>-2.966793858536923</v>
       </c>
       <c r="G53">
-        <v>-11.23020256680656</v>
+        <v>-12.32604610903395</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.19249083385561</v>
       </c>
       <c r="E54">
-        <v>-20.14991813513366</v>
+        <v>-21.88942274180404</v>
       </c>
       <c r="F54">
-        <v>-3.624282320017335</v>
+        <v>-2.051891055003967</v>
       </c>
       <c r="G54">
-        <v>-10.00578405692495</v>
+        <v>-11.29234150657868</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.27623690621192</v>
       </c>
       <c r="E55">
-        <v>-20.38630900680806</v>
+        <v>-24.99326146903134</v>
       </c>
       <c r="F55">
-        <v>-3.415534562879263</v>
+        <v>-2.8359706229802</v>
       </c>
       <c r="G55">
-        <v>-10.79858688157854</v>
+        <v>-11.74472755452009</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.377106087249596</v>
       </c>
       <c r="E56">
-        <v>-19.96812254609573</v>
+        <v>-22.42321661545818</v>
       </c>
       <c r="F56">
-        <v>-3.767566686414372</v>
+        <v>-2.614442813551737</v>
       </c>
       <c r="G56">
-        <v>-10.69311952178844</v>
+        <v>-11.93077690328159</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.492590869697755</v>
       </c>
       <c r="E57">
-        <v>-20.30322962266333</v>
+        <v>-21.18631828195112</v>
       </c>
       <c r="F57">
-        <v>-3.808485551010459</v>
+        <v>-3.165172940894154</v>
       </c>
       <c r="G57">
-        <v>-11.21540773879155</v>
+        <v>-11.59190615133625</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.618504809206513</v>
       </c>
       <c r="E58">
-        <v>-20.69335765842414</v>
+        <v>-20.59306554457626</v>
       </c>
       <c r="F58">
-        <v>-3.541911122217758</v>
+        <v>-2.853502190693049</v>
       </c>
       <c r="G58">
-        <v>-11.7222125343075</v>
+        <v>-11.30546119855081</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.749173587013177</v>
       </c>
       <c r="E59">
-        <v>-20.06548926573465</v>
+        <v>-22.70104755277677</v>
       </c>
       <c r="F59">
-        <v>-4.033076663094475</v>
+        <v>-3.562974848536144</v>
       </c>
       <c r="G59">
-        <v>-9.659908190618516</v>
+        <v>-12.14327088981079</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.878664456683373</v>
       </c>
       <c r="E60">
-        <v>-19.70771264828464</v>
+        <v>-21.35502658110688</v>
       </c>
       <c r="F60">
-        <v>-3.838565228140915</v>
+        <v>-2.83186357739712</v>
       </c>
       <c r="G60">
-        <v>-9.756245065811308</v>
+        <v>-12.72068300058831</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.002035469526484</v>
       </c>
       <c r="E61">
-        <v>-20.99771186800565</v>
+        <v>-21.48877506092342</v>
       </c>
       <c r="F61">
-        <v>-4.201643630992354</v>
+        <v>-3.14443227786286</v>
       </c>
       <c r="G61">
-        <v>-11.10134951332704</v>
+        <v>-12.72569847708031</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.113427482301638</v>
       </c>
       <c r="E62">
-        <v>-21.75086049411734</v>
+        <v>-22.4369831764415</v>
       </c>
       <c r="F62">
-        <v>-3.893305402852711</v>
+        <v>-3.210650311307847</v>
       </c>
       <c r="G62">
-        <v>-10.96160807556887</v>
+        <v>-11.9986563290188</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.205980659645454</v>
       </c>
       <c r="E63">
-        <v>-21.92570034707949</v>
+        <v>-22.34637746849603</v>
       </c>
       <c r="F63">
-        <v>-3.997222436799104</v>
+        <v>-3.306572771449821</v>
       </c>
       <c r="G63">
-        <v>-10.92093471307338</v>
+        <v>-11.94208903738928</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.277379753291782</v>
       </c>
       <c r="E64">
-        <v>-21.86599694576236</v>
+        <v>-21.80895175868774</v>
       </c>
       <c r="F64">
-        <v>-3.81285933089724</v>
+        <v>-3.531190391290727</v>
       </c>
       <c r="G64">
-        <v>-9.868326895588872</v>
+        <v>-11.99319723942454</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.325143409586449</v>
       </c>
       <c r="E65">
-        <v>-22.29290071893945</v>
+        <v>-22.03423428362132</v>
       </c>
       <c r="F65">
-        <v>-3.879189193941605</v>
+        <v>-3.593370962014469</v>
       </c>
       <c r="G65">
-        <v>-11.23125863083358</v>
+        <v>-12.2897426666503</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.348392259957442</v>
       </c>
       <c r="E66">
-        <v>-21.46510925575933</v>
+        <v>-21.36402918743412</v>
       </c>
       <c r="F66">
-        <v>-3.692934096891747</v>
+        <v>-3.495781826658062</v>
       </c>
       <c r="G66">
-        <v>-11.01696701807656</v>
+        <v>-12.04978108378177</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.346877360991273</v>
       </c>
       <c r="E67">
-        <v>-21.37597983034037</v>
+        <v>-23.94402309840213</v>
       </c>
       <c r="F67">
-        <v>-4.290478579635976</v>
+        <v>-3.699330749976165</v>
       </c>
       <c r="G67">
-        <v>-11.5162932912193</v>
+        <v>-12.31626675751094</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.323835668960668</v>
       </c>
       <c r="E68">
-        <v>-21.66366019862564</v>
+        <v>-22.84400242025091</v>
       </c>
       <c r="F68">
-        <v>-3.560679442462987</v>
+        <v>-3.177522242135089</v>
       </c>
       <c r="G68">
-        <v>-9.763763314730992</v>
+        <v>-12.75518550619859</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.283650010109058</v>
       </c>
       <c r="E69">
-        <v>-22.52653827841719</v>
+        <v>-22.64264382349985</v>
       </c>
       <c r="F69">
-        <v>-3.852128087626951</v>
+        <v>-3.619073545788532</v>
       </c>
       <c r="G69">
-        <v>-10.6071645174068</v>
+        <v>-11.89828389881364</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.230358210476891</v>
       </c>
       <c r="E70">
-        <v>-22.16023001593673</v>
+        <v>-22.4707520071167</v>
       </c>
       <c r="F70">
-        <v>-4.239625933145518</v>
+        <v>-3.035573203991366</v>
       </c>
       <c r="G70">
-        <v>-11.10178650533823</v>
+        <v>-10.83943901353314</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.167967259813158</v>
       </c>
       <c r="E71">
-        <v>-21.82272284814506</v>
+        <v>-24.38851999309902</v>
       </c>
       <c r="F71">
-        <v>-4.400878416876678</v>
+        <v>-4.27014878683647</v>
       </c>
       <c r="G71">
-        <v>-8.902279912319687</v>
+        <v>-11.94268162504081</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.10256670261266</v>
       </c>
       <c r="E72">
-        <v>-20.92227654798588</v>
+        <v>-22.06325274506247</v>
       </c>
       <c r="F72">
-        <v>-4.248235155562813</v>
+        <v>-3.115557046936075</v>
       </c>
       <c r="G72">
-        <v>-10.69809196118842</v>
+        <v>-12.90054162919137</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.038620927940348</v>
       </c>
       <c r="E73">
-        <v>-22.95230540461836</v>
+        <v>-22.66597905006137</v>
       </c>
       <c r="F73">
-        <v>-3.970755269912257</v>
+        <v>-3.949275703157666</v>
       </c>
       <c r="G73">
-        <v>-12.40851841950827</v>
+        <v>-11.78260019548935</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.979408091421584</v>
       </c>
       <c r="E74">
-        <v>-23.02451645114467</v>
+        <v>-24.18118833913185</v>
       </c>
       <c r="F74">
-        <v>-4.368737761648057</v>
+        <v>-3.612552637593695</v>
       </c>
       <c r="G74">
-        <v>-11.27673559490655</v>
+        <v>-12.68990154816417</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.925152025379809</v>
       </c>
       <c r="E75">
-        <v>-23.18933479112784</v>
+        <v>-24.88370409736377</v>
       </c>
       <c r="F75">
-        <v>-4.095161143199492</v>
+        <v>-3.812295212695934</v>
       </c>
       <c r="G75">
-        <v>-11.29522168119784</v>
+        <v>-12.04735776444702</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.877493316995712</v>
       </c>
       <c r="E76">
-        <v>-22.86301295413511</v>
+        <v>-26.07205718950861</v>
       </c>
       <c r="F76">
-        <v>-4.204171808305698</v>
+        <v>-3.311504042598687</v>
       </c>
       <c r="G76">
-        <v>-11.19197569746459</v>
+        <v>-10.32662226731788</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.835076637229189</v>
       </c>
       <c r="E77">
-        <v>-22.4850438710849</v>
+        <v>-23.02724259249728</v>
       </c>
       <c r="F77">
-        <v>-4.368929942885506</v>
+        <v>-3.945064283281833</v>
       </c>
       <c r="G77">
-        <v>-10.8362741319976</v>
+        <v>-12.02327685619436</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.79395267570832</v>
       </c>
       <c r="E78">
-        <v>-23.92738095642395</v>
+        <v>-24.63326589931758</v>
       </c>
       <c r="F78">
-        <v>-4.674680351258804</v>
+        <v>-4.612206538474471</v>
       </c>
       <c r="G78">
-        <v>-10.85218461385934</v>
+        <v>-12.45299890937392</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.750328129364</v>
       </c>
       <c r="E79">
-        <v>-22.72356765401692</v>
+        <v>-24.45824943586913</v>
       </c>
       <c r="F79">
-        <v>-4.545522134181708</v>
+        <v>-4.05760213678916</v>
       </c>
       <c r="G79">
-        <v>-12.162088030656</v>
+        <v>-12.92484103344962</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.701425355671731</v>
       </c>
       <c r="E80">
-        <v>-23.25509729066723</v>
+        <v>-25.48003619706384</v>
       </c>
       <c r="F80">
-        <v>-5.114923662783227</v>
+        <v>-3.712192810639433</v>
       </c>
       <c r="G80">
-        <v>-11.95283506820975</v>
+        <v>-12.83831330468969</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.644330575391947</v>
       </c>
       <c r="E81">
-        <v>-25.32547937918205</v>
+        <v>-25.12573744765173</v>
       </c>
       <c r="F81">
-        <v>-4.053756026937962</v>
+        <v>-4.472713609680048</v>
       </c>
       <c r="G81">
-        <v>-11.70869557687066</v>
+        <v>-12.26699259770443</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.576874902354974</v>
       </c>
       <c r="E82">
-        <v>-25.43733268717151</v>
+        <v>-27.57752120251457</v>
       </c>
       <c r="F82">
-        <v>-4.160146565949113</v>
+        <v>-4.296115619812027</v>
       </c>
       <c r="G82">
-        <v>-10.70640805158307</v>
+        <v>-12.40053007312201</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.497063923071507</v>
       </c>
       <c r="E83">
-        <v>-24.78510563279476</v>
+        <v>-26.98222159488825</v>
       </c>
       <c r="F83">
-        <v>-4.625977318178609</v>
+        <v>-4.192871220196707</v>
       </c>
       <c r="G83">
-        <v>-11.57222164755974</v>
+        <v>-12.54416802297991</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.407547653775861</v>
       </c>
       <c r="E84">
-        <v>-26.10631509537664</v>
+        <v>-26.27299010970295</v>
       </c>
       <c r="F84">
-        <v>-4.809276800335279</v>
+        <v>-4.964600658564603</v>
       </c>
       <c r="G84">
-        <v>-12.32385121734141</v>
+        <v>-11.80363209130034</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.310399297726614</v>
       </c>
       <c r="E85">
-        <v>-26.71088448929666</v>
+        <v>-26.29190554563299</v>
       </c>
       <c r="F85">
-        <v>-4.865359758607013</v>
+        <v>-4.210526214652574</v>
       </c>
       <c r="G85">
-        <v>-12.39557418644972</v>
+        <v>-12.83542650897945</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.207880817570056</v>
       </c>
       <c r="E86">
-        <v>-25.47554395084823</v>
+        <v>-29.89973173059595</v>
       </c>
       <c r="F86">
-        <v>-5.317471089911344</v>
+        <v>-5.126094197209977</v>
       </c>
       <c r="G86">
-        <v>-12.77771707913887</v>
+        <v>-11.40052351371098</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.105384541042122</v>
       </c>
       <c r="E87">
-        <v>-27.60686118561027</v>
+        <v>-29.5050299360874</v>
       </c>
       <c r="F87">
-        <v>-4.667582070984215</v>
+        <v>-4.637789008975128</v>
       </c>
       <c r="G87">
-        <v>-12.1405661741052</v>
+        <v>-12.97902804283641</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.009216201204808</v>
       </c>
       <c r="E88">
-        <v>-27.87140558019036</v>
+        <v>-30.81075881027405</v>
       </c>
       <c r="F88">
-        <v>-4.716358828763259</v>
+        <v>-4.65609095837258</v>
       </c>
       <c r="G88">
-        <v>-11.73247853602478</v>
+        <v>-12.16880181700965</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.925897421200027</v>
       </c>
       <c r="E89">
-        <v>-30.57104177444102</v>
+        <v>-29.6780719848685</v>
       </c>
       <c r="F89">
-        <v>-5.358219310822455</v>
+        <v>-5.393856504858292</v>
       </c>
       <c r="G89">
-        <v>-12.77726022385446</v>
+        <v>-11.9388877398528</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.861375366174677</v>
       </c>
       <c r="E90">
-        <v>-30.45122740914608</v>
+        <v>-31.52490368975768</v>
       </c>
       <c r="F90">
-        <v>-5.21135805398013</v>
+        <v>-5.010881545359011</v>
       </c>
       <c r="G90">
-        <v>-13.22567692769428</v>
+        <v>-12.73748070865457</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.821328240604609</v>
       </c>
       <c r="E91">
-        <v>-32.88364740915213</v>
+        <v>-30.88315099576067</v>
       </c>
       <c r="F91">
-        <v>-4.944625407013495</v>
+        <v>-4.688419653001636</v>
       </c>
       <c r="G91">
-        <v>-12.2773082576048</v>
+        <v>-13.71374238018518</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.812187786864391</v>
       </c>
       <c r="E92">
-        <v>-32.25436613257224</v>
+        <v>-34.05090686936924</v>
       </c>
       <c r="F92">
-        <v>-5.662397477865239</v>
+        <v>-4.837056101188161</v>
       </c>
       <c r="G92">
-        <v>-11.76139946185586</v>
+        <v>-13.57163721291196</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.837868873124483</v>
       </c>
       <c r="E93">
-        <v>-33.55911912061024</v>
+        <v>-33.48543179155743</v>
       </c>
       <c r="F93">
-        <v>-5.585404041244637</v>
+        <v>-5.517612109734331</v>
       </c>
       <c r="G93">
-        <v>-12.19965610143565</v>
+        <v>-13.03503254172427</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.898648030749029</v>
       </c>
       <c r="E94">
-        <v>-36.00642874315351</v>
+        <v>-33.53519972090173</v>
       </c>
       <c r="F94">
-        <v>-5.591751820652289</v>
+        <v>-5.228817553728936</v>
       </c>
       <c r="G94">
-        <v>-13.13464023590986</v>
+        <v>-13.17466804202519</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.997133783033164</v>
       </c>
       <c r="E95">
-        <v>-36.3703323859359</v>
+        <v>-37.22789630147944</v>
       </c>
       <c r="F95">
-        <v>-6.212549404760503</v>
+        <v>-5.709928371070472</v>
       </c>
       <c r="G95">
-        <v>-12.54525719246233</v>
+        <v>-13.11451874012217</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.135178065202247</v>
       </c>
       <c r="E96">
-        <v>-36.80656934404279</v>
+        <v>-40.1201737800164</v>
       </c>
       <c r="F96">
-        <v>-5.779113616552286</v>
+        <v>-6.308251519173332</v>
       </c>
       <c r="G96">
-        <v>-13.35642692376779</v>
+        <v>-15.18859041793049</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.309421483506732</v>
       </c>
       <c r="E97">
-        <v>-38.20171067327389</v>
+        <v>-41.37593094352841</v>
       </c>
       <c r="F97">
-        <v>-5.765743766671102</v>
+        <v>-5.806826648012944</v>
       </c>
       <c r="G97">
-        <v>-12.80156955974932</v>
+        <v>-13.1312800321875</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.522272097982994</v>
       </c>
       <c r="E98">
-        <v>-40.53448839545216</v>
+        <v>-42.84312029422154</v>
       </c>
       <c r="F98">
-        <v>-5.948103880192997</v>
+        <v>-6.209888688662711</v>
       </c>
       <c r="G98">
-        <v>-12.63709503626725</v>
+        <v>-13.13417675953436</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.764553642641523</v>
       </c>
       <c r="E99">
-        <v>-44.02613205127434</v>
+        <v>-41.35196173060581</v>
       </c>
       <c r="F99">
-        <v>-6.00771651196806</v>
+        <v>-6.764366350135393</v>
       </c>
       <c r="G99">
-        <v>-12.47669248379848</v>
+        <v>-14.29488382051269</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.045561226724642</v>
       </c>
       <c r="E100">
-        <v>-44.80858669692666</v>
+        <v>-46.38839013924255</v>
       </c>
       <c r="F100">
-        <v>-6.297572206616441</v>
+        <v>-7.249363867330865</v>
       </c>
       <c r="G100">
-        <v>-14.09398336446202</v>
+        <v>-13.4321788267974</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.342320238213232</v>
       </c>
       <c r="E101">
-        <v>-45.40733247327282</v>
+        <v>-46.95860200086637</v>
       </c>
       <c r="F101">
-        <v>-6.703819734113673</v>
+        <v>-7.723870939737283</v>
       </c>
       <c r="G101">
-        <v>-13.50658499306528</v>
+        <v>-14.69017951062937</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.679645894059699</v>
       </c>
       <c r="E102">
-        <v>-47.47310457524784</v>
+        <v>-48.48328259332389</v>
       </c>
       <c r="F102">
-        <v>-6.763573188347213</v>
+        <v>-7.167301650572532</v>
       </c>
       <c r="G102">
-        <v>-14.50578046881919</v>
+        <v>-14.50893376344535</v>
       </c>
     </row>
   </sheetData>
